--- a/data set.xlsx
+++ b/data set.xlsx
@@ -5,17 +5,33 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\87775\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c05f9151591783fa/MEMM 1263/experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{1577E002-5D70-4C1C-A17F-A33CBCE3497F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:9_{1577E002-5D70-4C1C-A17F-A33CBCE3497F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{618D3990-D604-45E6-A145-41CD63D5E6D9}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CA6A2299-5D31-4E35-83A0-2F40271CD996}"/>
   </bookViews>
   <sheets>
     <sheet name="feeds (1)" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -58,6 +74,30 @@
     <t>status</t>
   </si>
   <si>
+    <t>time stamp</t>
+  </si>
+  <si>
+    <t>RMS @ 1 x RPM - X</t>
+  </si>
+  <si>
+    <t>RMS @ 1 x RPM - Y</t>
+  </si>
+  <si>
+    <t>RMS @ 1 x RPM - Z</t>
+  </si>
+  <si>
+    <t>Frequency @ 1 x RPM - X</t>
+  </si>
+  <si>
+    <t>Frequency @ 1 x RPM - Y</t>
+  </si>
+  <si>
+    <t>Frequency @ 1 x RPM - Z</t>
+  </si>
+  <si>
+    <t>not running</t>
+  </si>
+  <si>
     <t>2025-06-16T11:11:13+08:00</t>
   </si>
   <si>
@@ -91,6 +131,9 @@
     <t>2025-06-16T11:14:08+08:00</t>
   </si>
   <si>
+    <t>normally running</t>
+  </si>
+  <si>
     <t>2025-06-16T11:14:26+08:00</t>
   </si>
   <si>
@@ -160,6 +203,9 @@
     <t>2025-06-16T11:39:43+08:00</t>
   </si>
   <si>
+    <t>abnormally running</t>
+  </si>
+  <si>
     <t>2025-06-16T11:40:01+08:00</t>
   </si>
   <si>
@@ -209,36 +255,6 @@
   </si>
   <si>
     <t>2025-06-16T11:45:02+08:00</t>
-  </si>
-  <si>
-    <t>RMS @ 1 x RPM - X</t>
-  </si>
-  <si>
-    <t>RMS @ 1 x RPM - Y</t>
-  </si>
-  <si>
-    <t>RMS @ 1 x RPM - Z</t>
-  </si>
-  <si>
-    <t>Frequency @ 1 x RPM - X</t>
-  </si>
-  <si>
-    <t>Frequency @ 1 x RPM - Y</t>
-  </si>
-  <si>
-    <t>Frequency @ 1 x RPM - Z</t>
-  </si>
-  <si>
-    <t>time stamp</t>
-  </si>
-  <si>
-    <t>normally running</t>
-  </si>
-  <si>
-    <t>abnormally running</t>
-  </si>
-  <si>
-    <t>not running</t>
   </si>
 </sst>
 </file>
@@ -2694,16 +2710,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>425825</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>162485</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1197350</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>109257</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>44823</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>499782</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>63873</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2729,6 +2745,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3032,11 +3052,10 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.59765625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.06640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
@@ -3078,37 +3097,37 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A3" s="1" t="s">
-        <v>72</v>
+      <c r="A3" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C3">
         <v>642</v>
@@ -3133,9 +3152,9 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A4" s="1"/>
+      <c r="A4" s="2"/>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C4">
         <v>643</v>
@@ -3160,9 +3179,9 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A5" s="1"/>
+      <c r="A5" s="2"/>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C5">
         <v>644</v>
@@ -3187,9 +3206,9 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A6" s="1"/>
+      <c r="A6" s="2"/>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C6">
         <v>645</v>
@@ -3214,9 +3233,9 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A7" s="1"/>
+      <c r="A7" s="2"/>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>646</v>
@@ -3241,9 +3260,9 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A8" s="1"/>
+      <c r="A8" s="2"/>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C8">
         <v>647</v>
@@ -3268,9 +3287,9 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A9" s="1"/>
+      <c r="A9" s="2"/>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C9">
         <v>648</v>
@@ -3295,9 +3314,9 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A10" s="2"/>
+      <c r="A10" s="1"/>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C10">
         <v>649</v>
@@ -3322,9 +3341,9 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A11" s="2"/>
+      <c r="A11" s="1"/>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C11">
         <v>650</v>
@@ -3349,9 +3368,9 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A12" s="2"/>
+      <c r="A12" s="1"/>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C12">
         <v>651</v>
@@ -3376,9 +3395,9 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A13" s="2"/>
+      <c r="A13" s="1"/>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C13">
         <v>652</v>
@@ -3403,11 +3422,11 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A14" s="1" t="s">
-        <v>70</v>
+      <c r="A14" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C14">
         <v>653</v>
@@ -3432,9 +3451,9 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A15" s="1"/>
+      <c r="A15" s="2"/>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C15">
         <v>654</v>
@@ -3459,9 +3478,9 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A16" s="1"/>
+      <c r="A16" s="2"/>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C16">
         <v>655</v>
@@ -3486,9 +3505,9 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A17" s="1"/>
+      <c r="A17" s="2"/>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C17">
         <v>656</v>
@@ -3513,9 +3532,9 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A18" s="1"/>
+      <c r="A18" s="2"/>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C18">
         <v>657</v>
@@ -3540,9 +3559,9 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A19" s="1"/>
+      <c r="A19" s="2"/>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C19">
         <v>658</v>
@@ -3567,9 +3586,9 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A20" s="1"/>
+      <c r="A20" s="2"/>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C20">
         <v>659</v>
@@ -3594,9 +3613,9 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A21" s="1"/>
+      <c r="A21" s="2"/>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C21">
         <v>660</v>
@@ -3621,9 +3640,9 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A22" s="1"/>
+      <c r="A22" s="2"/>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C22">
         <v>661</v>
@@ -3648,9 +3667,9 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A23" s="1"/>
+      <c r="A23" s="2"/>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C23">
         <v>662</v>
@@ -3675,9 +3694,9 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A24" s="1"/>
+      <c r="A24" s="2"/>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C24">
         <v>663</v>
@@ -3702,9 +3721,9 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A25" s="1"/>
+      <c r="A25" s="2"/>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C25">
         <v>664</v>
@@ -3729,9 +3748,9 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A26" s="2"/>
+      <c r="A26" s="1"/>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C26">
         <v>665</v>
@@ -3756,9 +3775,9 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A27" s="2"/>
+      <c r="A27" s="1"/>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C27">
         <v>666</v>
@@ -3783,9 +3802,9 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A28" s="2"/>
+      <c r="A28" s="1"/>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C28">
         <v>667</v>
@@ -3810,9 +3829,9 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A29" s="2"/>
+      <c r="A29" s="1"/>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C29">
         <v>668</v>
@@ -3837,9 +3856,9 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A30" s="2"/>
+      <c r="A30" s="1"/>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C30">
         <v>669</v>
@@ -3864,9 +3883,9 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A31" s="2"/>
+      <c r="A31" s="1"/>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C31">
         <v>718</v>
@@ -3891,9 +3910,9 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A32" s="2"/>
+      <c r="A32" s="1"/>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C32">
         <v>719</v>
@@ -3918,9 +3937,9 @@
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A33" s="2"/>
+      <c r="A33" s="1"/>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C33">
         <v>736</v>
@@ -3945,9 +3964,9 @@
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A34" s="2"/>
+      <c r="A34" s="1"/>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C34">
         <v>737</v>
@@ -3972,9 +3991,9 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A35" s="2"/>
+      <c r="A35" s="1"/>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C35">
         <v>738</v>
@@ -3999,9 +4018,9 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A36" s="2"/>
+      <c r="A36" s="1"/>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C36">
         <v>739</v>
@@ -4026,11 +4045,11 @@
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A37" s="1" t="s">
-        <v>71</v>
+      <c r="A37" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C37">
         <v>740</v>
@@ -4055,9 +4074,9 @@
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A38" s="1"/>
+      <c r="A38" s="2"/>
       <c r="B38" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C38">
         <v>741</v>
@@ -4082,9 +4101,9 @@
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A39" s="1"/>
+      <c r="A39" s="2"/>
       <c r="B39" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C39">
         <v>742</v>
@@ -4109,9 +4128,9 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A40" s="2"/>
+      <c r="A40" s="1"/>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C40">
         <v>743</v>
@@ -4136,9 +4155,9 @@
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A41" s="2"/>
+      <c r="A41" s="1"/>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C41">
         <v>744</v>
@@ -4163,9 +4182,9 @@
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A42" s="2"/>
+      <c r="A42" s="1"/>
       <c r="B42" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C42">
         <v>745</v>
@@ -4190,9 +4209,9 @@
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A43" s="2"/>
+      <c r="A43" s="1"/>
       <c r="B43" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C43">
         <v>746</v>
@@ -4217,9 +4236,9 @@
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A44" s="2"/>
+      <c r="A44" s="1"/>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C44">
         <v>747</v>
@@ -4244,9 +4263,9 @@
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A45" s="2"/>
+      <c r="A45" s="1"/>
       <c r="B45" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C45">
         <v>748</v>
@@ -4271,9 +4290,9 @@
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A46" s="2"/>
+      <c r="A46" s="1"/>
       <c r="B46" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C46">
         <v>749</v>
@@ -4298,9 +4317,9 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A47" s="2"/>
+      <c r="A47" s="1"/>
       <c r="B47" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C47">
         <v>750</v>
@@ -4325,9 +4344,9 @@
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A48" s="2"/>
+      <c r="A48" s="1"/>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C48">
         <v>751</v>
@@ -4353,7 +4372,7 @@
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C49">
         <v>752</v>
@@ -4379,7 +4398,7 @@
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C50">
         <v>753</v>
@@ -4405,7 +4424,7 @@
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C51">
         <v>754</v>
@@ -4431,7 +4450,7 @@
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C52">
         <v>755</v>
@@ -4457,7 +4476,7 @@
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C53">
         <v>756</v>
